--- a/Attendance_18Aug2025.xlsx
+++ b/Attendance_18Aug2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D05D096A-99DE-4762-B3BB-00CAB96556ED}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299DC5F0-8E93-481F-99D1-D8F3AE3458DF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{6EEB4539-9F63-46D1-BCFC-2794E541BBAB}"/>
   </bookViews>
@@ -24,44 +24,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Jagadees waran</author>
-  </authors>
-  <commentList>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{22CC1AEE-41D8-4E93-9E5D-F988212A5F0C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Sick Room</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{5FDF22F2-8897-4A70-AB12-17373711EB4B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Sick Room</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="86">
   <si>
@@ -327,7 +289,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,13 +303,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -719,7 +674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE372C8C-B17D-4723-96BF-08C853472E99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE372C8C-B17D-4723-96BF-08C853472E99}">
   <dimension ref="B2:E43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -979,7 +934,7 @@
         <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
@@ -1023,7 +978,7 @@
         <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
@@ -1193,6 +1148,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Attendance_18Aug2025.xlsx
+++ b/Attendance_18Aug2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299DC5F0-8E93-481F-99D1-D8F3AE3458DF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62C8CA3-60EC-4B66-8CED-2264325B9514}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{6EEB4539-9F63-46D1-BCFC-2794E541BBAB}"/>
   </bookViews>
@@ -24,8 +24,46 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Jagadees waran</author>
+  </authors>
+  <commentList>
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{5A824F9B-0184-46B4-BF9F-04F1F495D676}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>11:29 am</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E39" authorId="0" shapeId="0" xr:uid="{CC3D7CF5-43E5-4F7E-8B24-6DB6A36270C9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>11:18 am</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="86">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -289,7 +327,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +342,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -313,7 +358,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -336,36 +381,27 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -674,8 +710,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE372C8C-B17D-4723-96BF-08C853472E99}">
-  <dimension ref="B2:E43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE372C8C-B17D-4723-96BF-08C853472E99}">
+  <dimension ref="B2:E45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -688,10 +724,10 @@
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>0.38541666666666669</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="4">
         <v>0.45833333333333331</v>
       </c>
     </row>
@@ -702,7 +738,10 @@
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -713,7 +752,10 @@
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -724,7 +766,10 @@
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -735,7 +780,10 @@
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -746,7 +794,10 @@
       <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -757,7 +808,10 @@
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -768,7 +822,10 @@
       <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -779,7 +836,10 @@
       <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -790,7 +850,10 @@
       <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -801,7 +864,10 @@
       <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -812,7 +878,10 @@
       <c r="C13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -823,7 +892,10 @@
       <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -834,7 +906,10 @@
       <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -845,308 +920,416 @@
       <c r="C16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D16" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D25" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D31" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D32" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D33" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D34" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D35" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D36" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D37" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D39" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D40" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="4" t="s">
+      <c r="D40" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D42" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D42" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D43" t="s">
-        <v>84</v>
+      <c r="D43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D45">
+        <f>COUNTIF(D3:D43,"=P")</f>
+        <v>28</v>
+      </c>
+      <c r="E45">
+        <f>COUNTIF(E3:E43,"=P")</f>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D3:E43">
+    <cfRule type="iconSet" priority="2">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>